--- a/BatalhaDePontos.xlsx
+++ b/BatalhaDePontos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projetos\Python\1ESPI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patri\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7FD4C3AE-0C1B-41E4-AD56-A112A5AE41BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC5FAF72-EF45-42CF-8FB5-692A1C0BAF3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{9975B780-11C7-4C24-8927-6C524ACD7BA4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9975B780-11C7-4C24-8927-6C524ACD7BA4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,9 +28,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -74,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="54">
   <si>
     <t>Amanda Silva da Mata</t>
   </si>
@@ -176,13 +173,73 @@
   </si>
   <si>
     <t>Extra</t>
+  </si>
+  <si>
+    <t>Proporcional</t>
+  </si>
+  <si>
+    <t>Com os 20 pontos se estiver na lista</t>
+  </si>
+  <si>
+    <t>ARTHUR CARAM FIORESE HERRADA</t>
+  </si>
+  <si>
+    <t>DANIEL ROBERTO RIBEIRO DE FIGUEIREDO</t>
+  </si>
+  <si>
+    <t>FELIPE KENJI TAKATA</t>
+  </si>
+  <si>
+    <t>FELIPE RICARDO MOREIRA AGUIAR</t>
+  </si>
+  <si>
+    <t>FELIPE RORATO COSTA</t>
+  </si>
+  <si>
+    <t>FELIPE ROSSANO PEDROL</t>
+  </si>
+  <si>
+    <t>FELIPI BANDEIRA DE GODOY</t>
+  </si>
+  <si>
+    <t>GABRIEL FERREIRA FLAUSINO</t>
+  </si>
+  <si>
+    <t>GIOVANNA ANDRADE PAREJAS</t>
+  </si>
+  <si>
+    <t>GUSTAVO FERREIRA SILVA</t>
+  </si>
+  <si>
+    <t>JOAQUIM GASPARDO SOUZA MOURA</t>
+  </si>
+  <si>
+    <t>LEONARDO FERREIRA BARBOSA</t>
+  </si>
+  <si>
+    <t>LEONARDO GOMES GONÇALVES</t>
+  </si>
+  <si>
+    <t>LEONARDO PORTO SODRE</t>
+  </si>
+  <si>
+    <t>MATHEUS MEDEIROS DA CUNHA</t>
+  </si>
+  <si>
+    <t>MATHEUS PEREIRA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>MATHEUS SEQUEIRA FRANCO DA SILVA</t>
+  </si>
+  <si>
+    <t>Notas CP3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -251,8 +308,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -325,6 +388,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor rgb="FFDDEBF7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -353,7 +422,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -467,10 +536,12 @@
     <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -489,7 +560,7 @@
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
     <keyFlags>
       <key name="_Self">
@@ -551,9 +622,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -591,7 +662,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -697,7 +768,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -839,7 +910,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -847,15 +918,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15E42A73-C7D2-422C-A13B-BD8AB82A062C}">
-  <dimension ref="A1:T53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:T73"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="37.7109375" customWidth="1"/>
-    <col min="7" max="7" width="37.140625" customWidth="1"/>
-    <col min="20" max="20" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.6640625" customWidth="1"/>
+    <col min="7" max="7" width="37.109375" customWidth="1"/>
+    <col min="20" max="20" width="34.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1">
         <v>1</v>
       </c>
@@ -884,10 +955,10 @@
       </c>
       <c r="T1" t="str" cm="1">
         <f t="array" aca="1" ref="T1:T33" ca="1">_xlfn.SORTBY(C1:C33, _xlfn.RANDARRAY(ROWS(C1:C33)))</f>
-        <v>Giovanna Andrade Parejas</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+        <v>Leonardo Ferreira Barbosa</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2</v>
       </c>
@@ -911,10 +982,10 @@
       </c>
       <c r="T2" t="str">
         <f ca="1"/>
-        <v>Felipe Ricardo Moreira Aguiar</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+        <v>Arthur Caram Fiorese Herrada</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>3</v>
       </c>
@@ -938,10 +1009,10 @@
       </c>
       <c r="T3" t="str">
         <f ca="1"/>
-        <v>Jecky Cossio</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+        <v>Leonardo Gomes Gonçalves</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>4</v>
       </c>
@@ -965,10 +1036,10 @@
       </c>
       <c r="T4" t="str">
         <f ca="1"/>
-        <v>Daniel Roberto Ribeiro de Figueiredo</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+        <v>Laura Cardin Mirilli</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>5</v>
       </c>
@@ -992,10 +1063,10 @@
       </c>
       <c r="T5" t="str">
         <f ca="1"/>
-        <v>Laura Cardin Mirilli</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+        <v>Felipe Ricardo Moreira Aguiar</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>6</v>
       </c>
@@ -1019,10 +1090,10 @@
       </c>
       <c r="T6" t="str">
         <f ca="1"/>
-        <v>Matheus Medeiros da Cunha</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" ht="22.5" x14ac:dyDescent="0.25">
+        <v>Felipe Rorato Costa</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>7</v>
       </c>
@@ -1049,7 +1120,7 @@
         <v>Bruno Carreiro dos Santos</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>8</v>
       </c>
@@ -1073,10 +1144,10 @@
       </c>
       <c r="T8" t="str">
         <f ca="1"/>
-        <v>Kelso Oliveira do Amaral Sobrinho</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+        <v>Felipi Bandeira de Godoy</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>9</v>
       </c>
@@ -1100,10 +1171,10 @@
       </c>
       <c r="T9" t="str">
         <f ca="1"/>
-        <v>Beatriz Mantovani da Cruz</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+        <v>Matheus Pereira de Oliveira</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>10</v>
       </c>
@@ -1127,10 +1198,10 @@
       </c>
       <c r="T10" t="str">
         <f ca="1"/>
-        <v>Joaquim Gaspardo Souza Moura</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+        <v>Leonardo Porto Sodre</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>11</v>
       </c>
@@ -1154,10 +1225,10 @@
       </c>
       <c r="T11" t="str">
         <f ca="1"/>
-        <v>Matheus Sequeira Franco da Silva</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+        <v>Beatriz Mantovani da Cruz</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>12</v>
       </c>
@@ -1181,10 +1252,10 @@
       </c>
       <c r="T12" t="str">
         <f ca="1"/>
-        <v>Leonardo Ferreira Barbosa</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+        <v>Gabriel Ferreira Flausino</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>13</v>
       </c>
@@ -1208,10 +1279,10 @@
       </c>
       <c r="T13" t="str">
         <f ca="1"/>
-        <v>Felipe Kenji Takata</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+        <v>Gustavo Ducatti Bugelli</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>14</v>
       </c>
@@ -1235,10 +1306,10 @@
       </c>
       <c r="T14" t="str">
         <f ca="1"/>
-        <v>Bruce Li Yan Ting</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+        <v>Gustavo Moita de Lima</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>15</v>
       </c>
@@ -1262,10 +1333,10 @@
       </c>
       <c r="T15" t="str">
         <f ca="1"/>
-        <v>Leonardo Gomes Gonçalves</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+        <v>Amanda Silva da Mata</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>16</v>
       </c>
@@ -1289,10 +1360,10 @@
       </c>
       <c r="T16" t="str">
         <f ca="1"/>
-        <v>Gustavo Ducatti Bugelli</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+        <v>Laura Sampaio Neves</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>17</v>
       </c>
@@ -1313,10 +1384,10 @@
       </c>
       <c r="T17" t="str">
         <f ca="1"/>
-        <v>Eduardo Bechara Medeiros Craveiro</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+        <v>Gustavo Gaviolli Romero</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>18</v>
       </c>
@@ -1337,10 +1408,10 @@
       </c>
       <c r="T18" t="str">
         <f ca="1"/>
-        <v>Gabriel Ferreira Flausino</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+        <v>Gustavo Ferreira Silva</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>19</v>
       </c>
@@ -1352,10 +1423,10 @@
       </c>
       <c r="T19" t="str">
         <f ca="1"/>
-        <v>Leonardo Porto Sodre</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+        <v>Matheus Medeiros da Cunha</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>20</v>
       </c>
@@ -1367,10 +1438,10 @@
       </c>
       <c r="T20" t="str">
         <f ca="1"/>
-        <v>Felipi Bandeira de Godoy</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+        <v>Daniel Roberto Ribeiro de Figueiredo</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>21</v>
       </c>
@@ -1382,10 +1453,10 @@
       </c>
       <c r="T21" t="str">
         <f ca="1"/>
-        <v>Gustavo Gaviolli Romero</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+        <v>Jecky Cossio</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>22</v>
       </c>
@@ -1397,10 +1468,10 @@
       </c>
       <c r="T22" t="str">
         <f ca="1"/>
-        <v>Felipe Rorato Costa</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+        <v>Ricardo Salmerón Paulino de Souza</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>23</v>
       </c>
@@ -1412,10 +1483,10 @@
       </c>
       <c r="T23" t="str">
         <f ca="1"/>
-        <v>Gustavo Ferreira Silva</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+        <v>Giovanna Andrade Parejas</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>24</v>
       </c>
@@ -1430,7 +1501,7 @@
         <v>Felipe Rabelo</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>25</v>
       </c>
@@ -1442,10 +1513,10 @@
       </c>
       <c r="T25" t="str">
         <f ca="1"/>
-        <v>Matheus Pereira de Oliveira</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+        <v>Gustavo Ferreira Tavares</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26</v>
       </c>
@@ -1457,10 +1528,10 @@
       </c>
       <c r="T26" t="str">
         <f ca="1"/>
-        <v>Amanda Silva da Mata</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+        <v>Daniel Graciano dos Santos Ferreira</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>27</v>
       </c>
@@ -1472,10 +1543,10 @@
       </c>
       <c r="T27" t="str">
         <f ca="1"/>
-        <v>Daniel Graciano dos Santos Ferreira</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+        <v>Joaquim Gaspardo Souza Moura</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>28</v>
       </c>
@@ -1487,10 +1558,10 @@
       </c>
       <c r="T28" t="str">
         <f ca="1"/>
-        <v>Gustavo Moita de Lima</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+        <v>Felipe Rossano Pedrol</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>29</v>
       </c>
@@ -1502,10 +1573,10 @@
       </c>
       <c r="T29" t="str">
         <f ca="1"/>
-        <v>Laura Sampaio Neves</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+        <v>Kelso Oliveira do Amaral Sobrinho</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>30</v>
       </c>
@@ -1517,10 +1588,10 @@
       </c>
       <c r="T30" t="str">
         <f ca="1"/>
-        <v>Ricardo Salmerón Paulino de Souza</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+        <v>Bruce Li Yan Ting</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>31</v>
       </c>
@@ -1532,10 +1603,10 @@
       </c>
       <c r="T31" t="str">
         <f ca="1"/>
-        <v>Gustavo Ferreira Tavares</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+        <v>Felipe Kenji Takata</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>32</v>
       </c>
@@ -1547,10 +1618,10 @@
       </c>
       <c r="T32" t="str">
         <f ca="1"/>
-        <v>Felipe Rossano Pedrol</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+        <v>Eduardo Bechara Medeiros Craveiro</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>33</v>
       </c>
@@ -1562,138 +1633,514 @@
       </c>
       <c r="T33" t="str">
         <f ca="1"/>
-        <v>Arthur Caram Fiorese Herrada</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+        <v>Matheus Sequeira Franco da Silva</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="C38" s="41" t="s">
         <v>15</v>
       </c>
       <c r="G38" s="49" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="J38" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="C39" s="35" t="s">
         <v>1</v>
       </c>
       <c r="G39" s="50" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="J39" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="C40" s="47" t="s">
         <v>17</v>
       </c>
       <c r="G40" s="49" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="J40" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="C41" s="45" t="s">
         <v>18</v>
       </c>
       <c r="G41" s="49" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="J41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="C42" s="36" t="s">
         <v>4</v>
       </c>
       <c r="G42" s="50" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="J42" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="C43" s="37" t="s">
         <v>6</v>
       </c>
       <c r="G43" s="50" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="J43" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="C44" s="38" t="s">
         <v>22</v>
       </c>
       <c r="G44" s="49" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="J44" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="C45" s="39" t="s">
         <v>8</v>
       </c>
       <c r="G45" s="50" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="J45" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="C46" s="40" t="s">
         <v>9</v>
       </c>
       <c r="G46" s="50" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="J46" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="C47" s="42" t="s">
         <v>11</v>
       </c>
       <c r="G47" s="50" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="J47" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="C48" s="43" t="s">
         <v>12</v>
       </c>
       <c r="G48" s="50" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="49" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="J48" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C49" s="44" t="s">
         <v>13</v>
       </c>
       <c r="G49" s="50" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="50" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="J49" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C50" s="34" t="s">
         <v>29</v>
       </c>
       <c r="G50" s="49" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="51" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="J50" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C51" s="46" t="s">
         <v>30</v>
       </c>
       <c r="G51" s="49" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="52" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="J51" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C52" s="33" t="s">
         <v>17</v>
       </c>
       <c r="G52" s="50" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="53" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="J52" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="53" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C53" s="48" t="s">
         <v>20</v>
       </c>
       <c r="G53" s="49" t="s">
         <v>20</v>
       </c>
+      <c r="J53" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="56" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C56" t="s">
+        <v>53</v>
+      </c>
+      <c r="E56" t="s">
+        <v>34</v>
+      </c>
+      <c r="F56" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="57" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C57" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="D57" s="51">
+        <v>100</v>
+      </c>
+      <c r="E57">
+        <f>D57*0.8</f>
+        <v>80</v>
+      </c>
+      <c r="F57">
+        <f>E57+20</f>
+        <v>100</v>
+      </c>
+      <c r="H57" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C58" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="D58" s="52">
+        <v>90</v>
+      </c>
+      <c r="E58">
+        <f t="shared" ref="E58:F73" si="0">D58*0.8</f>
+        <v>72</v>
+      </c>
+      <c r="F58">
+        <f>E58+20</f>
+        <v>92</v>
+      </c>
+      <c r="H58" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C59" s="51" t="s">
+        <v>38</v>
+      </c>
+      <c r="D59" s="51">
+        <v>95</v>
+      </c>
+      <c r="E59">
+        <f t="shared" si="0"/>
+        <v>76</v>
+      </c>
+      <c r="F59">
+        <f>E59+20</f>
+        <v>96</v>
+      </c>
+      <c r="H59" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C60" s="52" t="s">
+        <v>39</v>
+      </c>
+      <c r="D60" s="52">
+        <v>80</v>
+      </c>
+      <c r="E60">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="F60">
+        <v>64</v>
+      </c>
+      <c r="H60" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C61" s="51" t="s">
+        <v>40</v>
+      </c>
+      <c r="D61" s="51">
+        <v>50</v>
+      </c>
+      <c r="E61">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="F61">
+        <v>40</v>
+      </c>
+      <c r="H61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C62" s="52" t="s">
+        <v>41</v>
+      </c>
+      <c r="D62" s="52">
+        <v>90</v>
+      </c>
+      <c r="E62">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="F62">
+        <f t="shared" ref="F62:F72" si="1">E62+20</f>
+        <v>92</v>
+      </c>
+      <c r="H62" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C63" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="D63" s="51">
+        <v>85</v>
+      </c>
+      <c r="E63">
+        <f t="shared" si="0"/>
+        <v>68</v>
+      </c>
+      <c r="F63">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+      <c r="H63" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C64" s="52" t="s">
+        <v>43</v>
+      </c>
+      <c r="D64" s="52">
+        <v>95</v>
+      </c>
+      <c r="E64">
+        <f t="shared" si="0"/>
+        <v>76</v>
+      </c>
+      <c r="F64">
+        <f t="shared" si="1"/>
+        <v>96</v>
+      </c>
+      <c r="H64" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C65" s="51" t="s">
+        <v>44</v>
+      </c>
+      <c r="D65" s="51">
+        <v>100</v>
+      </c>
+      <c r="E65">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="F65">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="H65" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C66" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="D66" s="52">
+        <v>90</v>
+      </c>
+      <c r="E66">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="F66">
+        <f t="shared" si="1"/>
+        <v>92</v>
+      </c>
+      <c r="H66" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C67" s="51" t="s">
+        <v>46</v>
+      </c>
+      <c r="D67" s="51">
+        <v>100</v>
+      </c>
+      <c r="E67">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="F67">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="H67" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="68" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C68" s="52" t="s">
+        <v>47</v>
+      </c>
+      <c r="D68" s="52">
+        <v>100</v>
+      </c>
+      <c r="E68">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="F68">
+        <v>80</v>
+      </c>
+      <c r="H68" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="69" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C69" s="51" t="s">
+        <v>48</v>
+      </c>
+      <c r="D69" s="51">
+        <v>75</v>
+      </c>
+      <c r="E69">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="F69">
+        <v>60</v>
+      </c>
+      <c r="H69" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="70" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C70" s="52" t="s">
+        <v>49</v>
+      </c>
+      <c r="D70" s="52">
+        <v>70</v>
+      </c>
+      <c r="E70">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="F70">
+        <v>56</v>
+      </c>
+      <c r="H70" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="71" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C71" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="D71" s="51">
+        <v>85</v>
+      </c>
+      <c r="E71">
+        <f t="shared" si="0"/>
+        <v>68</v>
+      </c>
+      <c r="F71">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+      <c r="H71" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="72" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C72" s="52" t="s">
+        <v>51</v>
+      </c>
+      <c r="D72" s="52">
+        <v>95</v>
+      </c>
+      <c r="E72">
+        <f t="shared" si="0"/>
+        <v>76</v>
+      </c>
+      <c r="F72">
+        <f t="shared" si="1"/>
+        <v>96</v>
+      </c>
+      <c r="H72" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="73" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C73" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="D73" s="51">
+        <v>80</v>
+      </c>
+      <c r="E73">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="F73">
+        <v>64</v>
+      </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="J38:J53">
+    <sortCondition ref="J38:J53"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
